--- a/Data/Testdata/Unittests.xlsx
+++ b/Data/Testdata/Unittests.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github.com\rpapub\PurposefulPromethium\Data\Testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C521B79-CB7E-4D36-923C-1A2E66DF2C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EA5381-3BAA-47C0-9EAA-88DAD961B488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11835" xr2:uid="{0F59387B-8167-4962-A8A1-49C75F9DA195}"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{0F59387B-8167-4962-A8A1-49C75F9DA195}"/>
   </bookViews>
   <sheets>
     <sheet name="OpenBrowser" sheetId="1" r:id="rId1"/>
+    <sheet name="VerifyImapConn" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
   <si>
     <t>in_Environment</t>
   </si>
@@ -46,6 +47,18 @@
   </si>
   <si>
     <t>true</t>
+  </si>
+  <si>
+    <t>dev</t>
+  </si>
+  <si>
+    <t>in_ConfigFile</t>
+  </si>
+  <si>
+    <t>Data\Config_Dev.xlsx</t>
+  </si>
+  <si>
+    <t>in_MinMailmsgsCountExpected</t>
   </si>
 </sst>
 </file>
@@ -444,4 +457,47 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADAA743D-90C4-4034-A07B-93BE2630C4A8}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="20.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Data/Testdata/Unittests.xlsx
+++ b/Data/Testdata/Unittests.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github.com\rpapub\PurposefulPromethium\Data\Testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EA5381-3BAA-47C0-9EAA-88DAD961B488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD09FED0-44E4-439E-8157-A0BED2EB5D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{0F59387B-8167-4962-A8A1-49C75F9DA195}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11835" activeTab="2" xr2:uid="{0F59387B-8167-4962-A8A1-49C75F9DA195}"/>
   </bookViews>
   <sheets>
     <sheet name="OpenBrowser" sheetId="1" r:id="rId1"/>
     <sheet name="VerifyImapConn" sheetId="2" r:id="rId2"/>
+    <sheet name="Config" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="28">
   <si>
     <t>in_Environment</t>
   </si>
@@ -59,6 +60,66 @@
   </si>
   <si>
     <t>in_MinMailmsgsCountExpected</t>
+  </si>
+  <si>
+    <t>OrchestratorFolderPath</t>
+  </si>
+  <si>
+    <t>logF_BusinessProcessName</t>
+  </si>
+  <si>
+    <t>QueueConsumptionStrategy</t>
+  </si>
+  <si>
+    <t>Imap_Server</t>
+  </si>
+  <si>
+    <t>Imap_Port</t>
+  </si>
+  <si>
+    <t>Imap_Credentialname</t>
+  </si>
+  <si>
+    <t>Mailbox_FolderIncoming</t>
+  </si>
+  <si>
+    <t>Mailbox_Batchsize</t>
+  </si>
+  <si>
+    <t>Mailbox_FolderProcessing</t>
+  </si>
+  <si>
+    <t>Mailbox_FolderHandover2Human</t>
+  </si>
+  <si>
+    <t>Mailbox_FolderSuccessful</t>
+  </si>
+  <si>
+    <t>File_BasePathTemp</t>
+  </si>
+  <si>
+    <t>FTP_ServerHostname</t>
+  </si>
+  <si>
+    <t>FTP_ServerPort</t>
+  </si>
+  <si>
+    <t>FTP_CredentialName</t>
+  </si>
+  <si>
+    <t>FTP_RemotePathPristine</t>
+  </si>
+  <si>
+    <t>FTP_RemotePathTainted</t>
+  </si>
+  <si>
+    <t>in_ConfigItem</t>
+  </si>
+  <si>
+    <t>foo</t>
+  </si>
+  <si>
+    <t>false</t>
   </si>
 </sst>
 </file>
@@ -500,4 +561,284 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD2DB8F-8CD4-4CCE-9F1A-7FED9B15A02E}">
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Data/Testdata/Unittests.xlsx
+++ b/Data/Testdata/Unittests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github.com\rpapub\PurposefulPromethium\Data\Testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD09FED0-44E4-439E-8157-A0BED2EB5D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512FF058-1FD6-4E57-92F0-A52486132947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11835" activeTab="2" xr2:uid="{0F59387B-8167-4962-A8A1-49C75F9DA195}"/>
+    <workbookView xWindow="1575" yWindow="4065" windowWidth="21600" windowHeight="11835" activeTab="2" xr2:uid="{0F59387B-8167-4962-A8A1-49C75F9DA195}"/>
   </bookViews>
   <sheets>
     <sheet name="OpenBrowser" sheetId="1" r:id="rId1"/>

--- a/Data/Testdata/Unittests.xlsx
+++ b/Data/Testdata/Unittests.xlsx
@@ -8,15 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github.com\rpapub\PurposefulPromethium\Data\Testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512FF058-1FD6-4E57-92F0-A52486132947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17ADE22-86F0-4526-9E0D-CB5E7AEAE9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1575" yWindow="4065" windowWidth="21600" windowHeight="11835" activeTab="2" xr2:uid="{0F59387B-8167-4962-A8A1-49C75F9DA195}"/>
+    <workbookView xWindow="2970" yWindow="3180" windowWidth="21600" windowHeight="11835" activeTab="3" xr2:uid="{0F59387B-8167-4962-A8A1-49C75F9DA195}"/>
   </bookViews>
   <sheets>
     <sheet name="OpenBrowser" sheetId="1" r:id="rId1"/>
     <sheet name="VerifyImapConn" sheetId="2" r:id="rId2"/>
     <sheet name="Config" sheetId="3" r:id="rId3"/>
+    <sheet name="GenerateValidFilename" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">GenerateValidFilename!$A$1:$D$53</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="129">
   <si>
     <t>in_Environment</t>
   </si>
@@ -120,6 +124,309 @@
   </si>
   <si>
     <t>false</t>
+  </si>
+  <si>
+    <t>in_String</t>
+  </si>
+  <si>
+    <t>in_FileBasenameExpected</t>
+  </si>
+  <si>
+    <t>mLTT5</t>
+  </si>
+  <si>
+    <t>z7snnCDAnGCyDIcrSetx7QbVel</t>
+  </si>
+  <si>
+    <t>DZxUIUa73OvMOESDaZeJwCS</t>
+  </si>
+  <si>
+    <t>0maIz2oOAJrUI3sQShUMpG6BEQVQNjd</t>
+  </si>
+  <si>
+    <t>y5ciyP7ge9NXSAGYfura5NLQkY85XcIjdiFgh</t>
+  </si>
+  <si>
+    <t>HEiUjeonwaJLi6X3RGlfq2Dc8eV</t>
+  </si>
+  <si>
+    <t>CVExtgF0</t>
+  </si>
+  <si>
+    <t>i3ZLHZFWdBNbNbGOYmJMwbuZFgesWsWho5</t>
+  </si>
+  <si>
+    <t>k3ptVnnijmn4Pbov</t>
+  </si>
+  <si>
+    <t>m1McAQ3dqMz85t</t>
+  </si>
+  <si>
+    <t>12P0ltU3mz</t>
+  </si>
+  <si>
+    <t>5lOFwYlivbkkmttjlAuQHi6Jvy6tPHhn</t>
+  </si>
+  <si>
+    <t>ITMtsArLTCleBjscev0</t>
+  </si>
+  <si>
+    <t>Jw7HaOtdCxXmANabLUtoM0bznmix</t>
+  </si>
+  <si>
+    <t>txqPLHgGKEzxADmpfU2BWPPl9i4XT6w</t>
+  </si>
+  <si>
+    <t>iV98DdiIwUgj9hvMJkggtVZPVVp</t>
+  </si>
+  <si>
+    <t>DMw6qNsDKttHOsCmi4iVHVixvGo</t>
+  </si>
+  <si>
+    <t>2kBJrhbMjjdRjHYg</t>
+  </si>
+  <si>
+    <t>F8uZA4AcQmyBzGzxhKh</t>
+  </si>
+  <si>
+    <t>832u4ckqQoi3JmF2RO</t>
+  </si>
+  <si>
+    <t>22WCg3ScgraM5F1AlEpKFJl</t>
+  </si>
+  <si>
+    <t>fr9pQWnIcraK335</t>
+  </si>
+  <si>
+    <t>r54bkqreDLgRQcQX7</t>
+  </si>
+  <si>
+    <t>w5gxcGxAegux1T5vcIptInIQK</t>
+  </si>
+  <si>
+    <t>UsVKYlFHNCQd7AemtfP2OjZ3A</t>
+  </si>
+  <si>
+    <t>42(,LN:`}]r*GQNr-W{&gt;*O&amp;)BYx]H</t>
+  </si>
+  <si>
+    <t>&amp;E$wg]/SU!-=9UfB</t>
+  </si>
+  <si>
+    <t>)Ry7{0bt!_E~^:[]iE%"e#R{:RCP=</t>
+  </si>
+  <si>
+    <t>e]LBA6./o3m6a5)PCq`5&gt;*@\\AeLyHI;&amp;V#=DY"3</t>
+  </si>
+  <si>
+    <t>W4'gqE0'C'-FYHIu^[v+*(lv )ye*J[Z{[]8nUb3w%</t>
+  </si>
+  <si>
+    <t>u~={cWq!_eGLcD!auFP</t>
+  </si>
+  <si>
+    <t>E|Xf5tK3m:HwWeX2&amp;TGI&lt;</t>
+  </si>
+  <si>
+    <t>1@:xA{MO=)V'X@X;4 Q+rr</t>
+  </si>
+  <si>
+    <t>)DL"4J4b]jIYt}$/~W`.o&lt;Si{+wv9</t>
+  </si>
+  <si>
+    <t>ipzqTJ\\Xw58a?ZYv/4'0=6\\i@z$=!5&lt;2</t>
+  </si>
+  <si>
+    <t>}craygy|ME;-?u~6PHi)ERQj&lt;k)MIj$7Nj_w`d7iTkN-O5&lt;&amp;vhkAn*R#HnuM</t>
+  </si>
+  <si>
+    <t>7"&gt;1[|_$(hMp\\YpF}h|J5V</t>
+  </si>
+  <si>
+    <t>0MjB8-&amp;@3/%&lt;M&lt;o0wLaGy?JU?c5o|7!:rP</t>
+  </si>
+  <si>
+    <t>,"h.3` }wuh(Df};&gt;{=vTR|rn</t>
+  </si>
+  <si>
+    <t>`c|3Mh[-@&lt;zA:F^%</t>
+  </si>
+  <si>
+    <t>zF&amp;.b;$i.f3{S3ggd+&amp; *;ON2]UwQCQGx8x5\\H/,A`zt9RY~5N5]kL</t>
+  </si>
+  <si>
+    <t>3=[|@Y%U`M.c"G8</t>
+  </si>
+  <si>
+    <t>cS[H )C+S</t>
+  </si>
+  <si>
+    <t>Z7X#cfeVxenW-%1=)_/ ZO</t>
+  </si>
+  <si>
+    <t>v)V+Eq;{D&amp;xQn3}T</t>
+  </si>
+  <si>
+    <t>2IYO-O!\\H}BO-BinWLG*,LT8[:TQYjdCF1&amp;&lt;0</t>
+  </si>
+  <si>
+    <t>)4x7%g</t>
+  </si>
+  <si>
+    <t>D'e:8e3{svTUWc&amp;O</t>
+  </si>
+  <si>
+    <t>DZbZ!Ofr1K|EMbqdSm^MR-z pho_N\\&gt;b$qk_)Te_}U/=</t>
+  </si>
+  <si>
+    <t>^D6%+[13$dnmJh/u9r9d,gVRV&amp;)B8F=wB$@_H6Qrbw#]@wqpB/&gt;Eq,*+</t>
+  </si>
+  <si>
+    <t>abcdefghijklmnopqrstuvwxyzABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789abcdefghijklmnopqrstuvwxyzABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789abcdefghijklmnopqrstuvwxyzABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789abcdefghijklmnopqrstuvwxyzABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789________</t>
+  </si>
+  <si>
+    <t>abcdefghijklmnopqrstuvwxyzABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789abcdefghijklmnopqrstuvwxyzABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789abcdefghijklmnopqrstuvwxyzABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789abcdefghijklmnopqrstuvwxyzABCDEFGHIJKLMNOPQRSTUVWXYZ0123456789_______</t>
+  </si>
+  <si>
+    <t>42(,LN`}]rGQNr-W{O&amp;)BYx]H</t>
+  </si>
+  <si>
+    <t>&amp;E$wg]SU!-=9UfB</t>
+  </si>
+  <si>
+    <t>zF&amp;.b;$i.f3{S3ggd+&amp; ;ON2]UwQCQGx8x5H,A`zt9RY~5N5]kL</t>
+  </si>
+  <si>
+    <t>Z7X#cfeVxenW-%1=)_ ZO</t>
+  </si>
+  <si>
+    <t>)Ry7{0bt!_E~^[]iE%e#R{RCP=</t>
+  </si>
+  <si>
+    <t>D'e8e3{svTUWc&amp;O</t>
+  </si>
+  <si>
+    <t>)DL4J4b]jIYt}$~W`.oSi{+wv9</t>
+  </si>
+  <si>
+    <t>71[_$(hMpYpF}hJ5V</t>
+  </si>
+  <si>
+    <t>DZbZ!Ofr1KEMbqdSm^MR-z pho_Nb$qk_)Te_}U=</t>
+  </si>
+  <si>
+    <t>EXf5tK3mHwWeX2&amp;TGI</t>
+  </si>
+  <si>
+    <t>,h.3` }wuh(Df};{=vTRrn</t>
+  </si>
+  <si>
+    <t>ipzqTJXw58aZYv4'0=6i@z$=!52</t>
+  </si>
+  <si>
+    <t>`c3Mh[-@zAF^%</t>
+  </si>
+  <si>
+    <t>W4'gqE0'C'-FYHIu^[v+(lv )yeJ[Z{[]8nUb3w%</t>
+  </si>
+  <si>
+    <t>1@xA{MO=)V'X@X;4 Q+rr</t>
+  </si>
+  <si>
+    <t>}craygyME;-u~6PHi)ERQjk)MIj$7Nj_w`d7iTkN-O5&amp;vhkAnR#HnuM</t>
+  </si>
+  <si>
+    <t>0MjB8-&amp;@3%Mo0wLaGyJUc5o7!rP</t>
+  </si>
+  <si>
+    <t>3=[@Y%U`M.cG8</t>
+  </si>
+  <si>
+    <t>^D6%+[13$dnmJhu9r9d,gVRV&amp;)B8F=wB$@_H6Qrbw#]@wqpBEq,+</t>
+  </si>
+  <si>
+    <t>e]LBA6.o3m6a5)PCq`5@AeLyHI;&amp;V#=DY3</t>
+  </si>
+  <si>
+    <t>a          b</t>
+  </si>
+  <si>
+    <t>Example File Name.txt</t>
+  </si>
+  <si>
+    <t>keep</t>
+  </si>
+  <si>
+    <t>remove</t>
+  </si>
+  <si>
+    <t>ExampleFileName.txt</t>
+  </si>
+  <si>
+    <t>replace</t>
+  </si>
+  <si>
+    <t>Example_File_Name.txt</t>
+  </si>
+  <si>
+    <t>Longer Example File Name With Spaces.txt</t>
+  </si>
+  <si>
+    <t>LongerExampleFileNameWithSpaces.txt</t>
+  </si>
+  <si>
+    <t>Longer_Example_File_Name_With_Spaces.txt</t>
+  </si>
+  <si>
+    <t>Short Name</t>
+  </si>
+  <si>
+    <t>ShortName</t>
+  </si>
+  <si>
+    <t>Short_Name</t>
+  </si>
+  <si>
+    <t>in_spacePolicy</t>
+  </si>
+  <si>
+    <t>in_StatusIsSuccessExpected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Example File Name.txt  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Longer Example File Name With Spaces.txt  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Short Name  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Example File Name.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Longer Example File Name With Spaces.txt</t>
+  </si>
+  <si>
+    <t>__Short_Name__</t>
+  </si>
+  <si>
+    <t>__Example_File_Name.txt</t>
+  </si>
+  <si>
+    <t>__Longer_Example_File_Name_With_Spaces.txt</t>
+  </si>
+  <si>
+    <t>2IYO-O!H}BO-BinWLG,LT8[TQYjdCF1&amp;0</t>
+  </si>
+  <si>
+    <t>COM</t>
+  </si>
+  <si>
+    <t>COM1_file</t>
+  </si>
+  <si>
+    <t>COM1</t>
   </si>
 </sst>
 </file>
@@ -841,4 +1148,881 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFCA2BC2-1CC8-4FB6-A045-DFAFB67E0378}">
+  <dimension ref="A1:D73"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="64.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="45.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B30" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>64</v>
+      </c>
+      <c r="B38" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>66</v>
+      </c>
+      <c r="B40" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>67</v>
+      </c>
+      <c r="B41" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>68</v>
+      </c>
+      <c r="B42" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>69</v>
+      </c>
+      <c r="B43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D43" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" t="s">
+        <v>27</v>
+      </c>
+      <c r="D44" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B45" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>72</v>
+      </c>
+      <c r="B46" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>73</v>
+      </c>
+      <c r="B47" t="s">
+        <v>27</v>
+      </c>
+      <c r="D47" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>74</v>
+      </c>
+      <c r="B48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>75</v>
+      </c>
+      <c r="B49" t="s">
+        <v>27</v>
+      </c>
+      <c r="D49" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>76</v>
+      </c>
+      <c r="B50" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>77</v>
+      </c>
+      <c r="B51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>78</v>
+      </c>
+      <c r="B52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>79</v>
+      </c>
+      <c r="B53" t="s">
+        <v>27</v>
+      </c>
+      <c r="D53" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" t="s">
+        <v>105</v>
+      </c>
+      <c r="D55" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>103</v>
+      </c>
+      <c r="B56" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" t="s">
+        <v>107</v>
+      </c>
+      <c r="D56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>109</v>
+      </c>
+      <c r="B57" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" t="s">
+        <v>104</v>
+      </c>
+      <c r="D57" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" t="s">
+        <v>105</v>
+      </c>
+      <c r="D58" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>109</v>
+      </c>
+      <c r="B59" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" t="s">
+        <v>107</v>
+      </c>
+      <c r="D59" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>112</v>
+      </c>
+      <c r="B60" t="s">
+        <v>3</v>
+      </c>
+      <c r="C60" t="s">
+        <v>104</v>
+      </c>
+      <c r="D60" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>112</v>
+      </c>
+      <c r="B61" t="s">
+        <v>3</v>
+      </c>
+      <c r="C61" t="s">
+        <v>105</v>
+      </c>
+      <c r="D61" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>112</v>
+      </c>
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62" t="s">
+        <v>107</v>
+      </c>
+      <c r="D62" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>117</v>
+      </c>
+      <c r="B63" t="s">
+        <v>3</v>
+      </c>
+      <c r="C63" t="s">
+        <v>104</v>
+      </c>
+      <c r="D63" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>120</v>
+      </c>
+      <c r="B64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>105</v>
+      </c>
+      <c r="D64" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>117</v>
+      </c>
+      <c r="B65" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" t="s">
+        <v>107</v>
+      </c>
+      <c r="D65" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>118</v>
+      </c>
+      <c r="B66" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66" t="s">
+        <v>104</v>
+      </c>
+      <c r="D66" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>118</v>
+      </c>
+      <c r="B67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67" t="s">
+        <v>105</v>
+      </c>
+      <c r="D67" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>118</v>
+      </c>
+      <c r="B68" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" t="s">
+        <v>107</v>
+      </c>
+      <c r="D68" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>119</v>
+      </c>
+      <c r="B69" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" t="s">
+        <v>104</v>
+      </c>
+      <c r="D69" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>119</v>
+      </c>
+      <c r="B70" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" t="s">
+        <v>105</v>
+      </c>
+      <c r="D70" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>119</v>
+      </c>
+      <c r="B71" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71" t="s">
+        <v>107</v>
+      </c>
+      <c r="D71" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>126</v>
+      </c>
+      <c r="B72" t="s">
+        <v>27</v>
+      </c>
+      <c r="D72" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>128</v>
+      </c>
+      <c r="B73" t="s">
+        <v>27</v>
+      </c>
+      <c r="D73" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Data/Testdata/Unittests.xlsx
+++ b/Data/Testdata/Unittests.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github.com\rpapub\PurposefulPromethium\Data\Testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17ADE22-86F0-4526-9E0D-CB5E7AEAE9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8AA5BC6-DA38-4D99-88AF-A2677FA669B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2970" yWindow="3180" windowWidth="21600" windowHeight="11835" activeTab="3" xr2:uid="{0F59387B-8167-4962-A8A1-49C75F9DA195}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{0F59387B-8167-4962-A8A1-49C75F9DA195}"/>
   </bookViews>
   <sheets>
     <sheet name="OpenBrowser" sheetId="1" r:id="rId1"/>
     <sheet name="VerifyImapConn" sheetId="2" r:id="rId2"/>
     <sheet name="Config" sheetId="3" r:id="rId3"/>
     <sheet name="GenerateValidFilename" sheetId="4" r:id="rId4"/>
+    <sheet name="ParseRPAChallengeMessage" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">GenerateValidFilename!$A$1:$D$53</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="153">
   <si>
     <t>in_Environment</t>
   </si>
@@ -427,6 +428,78 @@
   </si>
   <si>
     <t>COM1</t>
+  </si>
+  <si>
+    <t>in_TestString</t>
+  </si>
+  <si>
+    <t>in_successRateExpected</t>
+  </si>
+  <si>
+    <t>in_completedFieldsExpected</t>
+  </si>
+  <si>
+    <t>in_totalFieldsExpected</t>
+  </si>
+  <si>
+    <t>in_executionTimeExpected</t>
+  </si>
+  <si>
+    <t>Your success rate is 80% ( 10 out of 50 fields) in 15000 milliseconds</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>Your success rate is 70% ( 7 out of 40 fields)</t>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t>Your success rate is 60% ( 6 out of fields) in 12000 milliseconds</t>
+  </si>
+  <si>
+    <t>Your success rate is 50% ( out of 30 fields) in 10000 milliseconds</t>
+  </si>
+  <si>
+    <t>Your success rate is 40% in 8000 milliseconds</t>
+  </si>
+  <si>
+    <t>Your success rate is ( 0 out of 20 fields) in 5000 milliseconds</t>
+  </si>
+  <si>
+    <t>Your success rate is 30% ( ) in 2000 milliseconds</t>
+  </si>
+  <si>
+    <t>Congratulations! Your success rate is 80% ( 10 out of 50 fields) in 15000 milliseconds</t>
+  </si>
+  <si>
+    <t>Congratulations! Your success rate is 70% ( 7 out of 40 fields)</t>
+  </si>
+  <si>
+    <t>Congratulations! Your success rate is 60% ( 6 out of fields) in 12000 milliseconds</t>
+  </si>
+  <si>
+    <t>Congratulations! Your success rate is 50% ( out of 30 fields) in 10000 milliseconds</t>
+  </si>
+  <si>
+    <t>Congratulations! Your success rate is 40% in 8000 milliseconds</t>
+  </si>
+  <si>
+    <t>Congratulations! Your success rate is ( 0 out of 20 fields) in 5000 milliseconds</t>
+  </si>
+  <si>
+    <t>Congratulations! Your success rate is 30% ( ) in 2000 milliseconds</t>
+  </si>
+  <si>
+    <t>Congratulations!</t>
+  </si>
+  <si>
+    <t>Congratulations! Processing completed with some warnings</t>
+  </si>
+  <si>
+    <t>in_successRateStringifiedExpected</t>
   </si>
 </sst>
 </file>
@@ -481,9 +554,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2025,4 +2099,330 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6AAFEA-0A8D-4E19-BB58-0E67BFD437DF}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="60.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="D2">
+        <v>0.8</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>50</v>
+      </c>
+      <c r="G2">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="D3">
+        <v>0.7</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="D4">
+        <v>0.6</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D5">
+        <v>0.5</v>
+      </c>
+      <c r="F5">
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="D6">
+        <v>0.4</v>
+      </c>
+      <c r="G6">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>20</v>
+      </c>
+      <c r="G7">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="D8">
+        <v>0.3</v>
+      </c>
+      <c r="G8">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="D10">
+        <v>0.8</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>50</v>
+      </c>
+      <c r="G10">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="D11">
+        <v>0.7</v>
+      </c>
+      <c r="E11">
+        <v>7</v>
+      </c>
+      <c r="F11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="D12">
+        <v>0.6</v>
+      </c>
+      <c r="E12">
+        <v>6</v>
+      </c>
+      <c r="G12">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D13">
+        <v>0.5</v>
+      </c>
+      <c r="F13">
+        <v>30</v>
+      </c>
+      <c r="G13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>147</v>
+      </c>
+      <c r="B14" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="D14">
+        <v>0.4</v>
+      </c>
+      <c r="G14">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>148</v>
+      </c>
+      <c r="B15" t="s">
+        <v>137</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>20</v>
+      </c>
+      <c r="G15">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="D16">
+        <v>0.3</v>
+      </c>
+      <c r="G16">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>